--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:27:53+00:00</t>
+    <t>2026-06-30T13:41:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0</t>
+    <t>2.4.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T13:41:45+00:00</t>
+    <t>2026-06-30T14:01:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:01:12+00:00</t>
+    <t>2026-06-30T14:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:55:37+00:00</t>
+    <t>2026-07-01T09:47:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T09:47:49+00:00</t>
+    <t>2026-07-01T11:47:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T11:47:31+00:00</t>
+    <t>2026-07-01T13:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:17:54+00:00</t>
+    <t>2026-07-01T14:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:33:44+00:00</t>
+    <t>2026-07-01T14:55:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T14:55:22+00:00</t>
+    <t>2026-07-01T15:33:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:33:30+00:00</t>
+    <t>2026-07-20T07:42:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.4.0-ballot</t>
+    <t>2.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T07:42:46+00:00</t>
+    <t>2026-07-22T13:04:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CodeSystem-tddui-basic-type.xlsx
+++ b/main/ig/CodeSystem-tddui-basic-type.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T13:04:03+00:00</t>
+    <t>2026-07-22T14:19:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
